--- a/Team-Data/2012-13/3-30-2012-13.xlsx
+++ b/Team-Data/2012-13/3-30-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F2" t="n">
         <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>0.554</v>
+        <v>0.548</v>
       </c>
       <c r="H2" t="n">
         <v>48.5</v>
@@ -685,19 +752,19 @@
         <v>0.465</v>
       </c>
       <c r="L2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="M2" t="n">
         <v>23.3</v>
       </c>
       <c r="N2" t="n">
-        <v>0.379</v>
+        <v>0.38</v>
       </c>
       <c r="O2" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="P2" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="Q2" t="n">
         <v>0.711</v>
@@ -706,7 +773,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="T2" t="n">
         <v>40.7</v>
@@ -715,7 +782,7 @@
         <v>24.6</v>
       </c>
       <c r="V2" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W2" t="n">
         <v>8.1</v>
@@ -727,7 +794,7 @@
         <v>4.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="AA2" t="n">
         <v>18.7</v>
@@ -736,10 +803,10 @@
         <v>97.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
@@ -748,7 +815,7 @@
         <v>12</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
         <v>11</v>
@@ -784,19 +851,19 @@
         <v>27</v>
       </c>
       <c r="AS2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU2" t="n">
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX2" t="n">
         <v>20</v>
@@ -805,7 +872,7 @@
         <v>7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BA2" t="n">
         <v>26</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>0.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AE3" t="n">
         <v>14</v>
@@ -936,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ3" t="n">
         <v>27</v>
@@ -954,7 +1021,7 @@
         <v>15</v>
       </c>
       <c r="AO3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP3" t="n">
         <v>19</v>
@@ -966,22 +1033,22 @@
         <v>29</v>
       </c>
       <c r="AS3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT3" t="n">
         <v>29</v>
       </c>
       <c r="AU3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY3" t="n">
         <v>11</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E4" t="n">
         <v>42</v>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>0.575</v>
+        <v>0.583</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
@@ -1046,7 +1113,7 @@
         <v>79.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L4" t="n">
         <v>7.7</v>
@@ -1061,31 +1128,31 @@
         <v>17.4</v>
       </c>
       <c r="P4" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.733</v>
+        <v>0.732</v>
       </c>
       <c r="R4" t="n">
         <v>12.8</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T4" t="n">
         <v>42.8</v>
       </c>
       <c r="U4" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V4" t="n">
         <v>14.8</v>
       </c>
       <c r="W4" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y4" t="n">
         <v>4.8</v>
@@ -1097,13 +1164,13 @@
         <v>21.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.09999999999999</v>
+        <v>96</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE4" t="n">
         <v>9</v>
@@ -1115,7 +1182,7 @@
         <v>9</v>
       </c>
       <c r="AH4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI4" t="n">
         <v>27</v>
@@ -1133,10 +1200,10 @@
         <v>7</v>
       </c>
       <c r="AN4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP4" t="n">
         <v>7</v>
@@ -1148,7 +1215,7 @@
         <v>6</v>
       </c>
       <c r="AS4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT4" t="n">
         <v>10</v>
@@ -1157,7 +1224,7 @@
         <v>28</v>
       </c>
       <c r="AV4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW4" t="n">
         <v>23</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E5" t="n">
         <v>17</v>
       </c>
       <c r="F5" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>0.233</v>
+        <v>0.236</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
@@ -1225,28 +1292,28 @@
         <v>34.3</v>
       </c>
       <c r="J5" t="n">
-        <v>81.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.422</v>
+        <v>0.421</v>
       </c>
       <c r="L5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="M5" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="N5" t="n">
         <v>0.337</v>
       </c>
       <c r="O5" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="P5" t="n">
         <v>25.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.746</v>
+        <v>0.747</v>
       </c>
       <c r="R5" t="n">
         <v>11.3</v>
@@ -1255,19 +1322,19 @@
         <v>28.9</v>
       </c>
       <c r="T5" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="U5" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="V5" t="n">
         <v>13.8</v>
       </c>
       <c r="W5" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Y5" t="n">
         <v>7.3</v>
@@ -1282,10 +1349,10 @@
         <v>93.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>-9.6</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1333,7 +1400,7 @@
         <v>29</v>
       </c>
       <c r="AT5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU5" t="n">
         <v>30</v>
@@ -1342,7 +1409,7 @@
         <v>5</v>
       </c>
       <c r="AW5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX5" t="n">
         <v>6</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -1389,52 +1456,52 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E6" t="n">
         <v>39</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G6" t="n">
-        <v>0.549</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>48.4</v>
       </c>
       <c r="I6" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J6" t="n">
-        <v>81.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0.345</v>
+        <v>0.34</v>
       </c>
       <c r="O6" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P6" t="n">
         <v>21</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.78</v>
+        <v>0.783</v>
       </c>
       <c r="R6" t="n">
         <v>12.8</v>
       </c>
       <c r="S6" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="T6" t="n">
         <v>43.5</v>
@@ -1455,40 +1522,40 @@
         <v>5.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>93</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AC6" t="n">
         <v>0.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF6" t="n">
         <v>10</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH6" t="n">
         <v>15</v>
       </c>
       <c r="AI6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ6" t="n">
         <v>14</v>
       </c>
       <c r="AK6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL6" t="n">
         <v>29</v>
@@ -1497,13 +1564,13 @@
         <v>29</v>
       </c>
       <c r="AN6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AQ6" t="n">
         <v>6</v>
@@ -1515,10 +1582,10 @@
         <v>14</v>
       </c>
       <c r="AT6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
         <v>12</v>
@@ -1539,10 +1606,10 @@
         <v>18</v>
       </c>
       <c r="BB6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-4.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE7" t="n">
         <v>28</v>
@@ -1691,7 +1758,7 @@
         <v>17</v>
       </c>
       <c r="AR7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS7" t="n">
         <v>30</v>
@@ -1703,10 +1770,10 @@
         <v>26</v>
       </c>
       <c r="AV7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX7" t="n">
         <v>29</v>
@@ -1718,7 +1785,7 @@
         <v>26</v>
       </c>
       <c r="BA7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB7" t="n">
         <v>17</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E8" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F8" t="n">
         <v>37</v>
       </c>
       <c r="G8" t="n">
-        <v>0.493</v>
+        <v>0.486</v>
       </c>
       <c r="H8" t="n">
         <v>48.8</v>
@@ -1771,16 +1838,16 @@
         <v>38.6</v>
       </c>
       <c r="J8" t="n">
-        <v>83.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L8" t="n">
         <v>7.5</v>
       </c>
       <c r="M8" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="N8" t="n">
         <v>0.373</v>
@@ -1795,7 +1862,7 @@
         <v>0.794</v>
       </c>
       <c r="R8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S8" t="n">
         <v>32.6</v>
@@ -1807,13 +1874,13 @@
         <v>23</v>
       </c>
       <c r="V8" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W8" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X8" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y8" t="n">
         <v>4.1</v>
@@ -1831,16 +1898,16 @@
         <v>-0.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE8" t="n">
         <v>17</v>
       </c>
       <c r="AF8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH8" t="n">
         <v>3</v>
@@ -1849,7 +1916,7 @@
         <v>4</v>
       </c>
       <c r="AJ8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK8" t="n">
         <v>9</v>
@@ -1867,7 +1934,7 @@
         <v>16</v>
       </c>
       <c r="AP8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ8" t="n">
         <v>2</v>
@@ -1897,7 +1964,7 @@
         <v>4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA8" t="n">
         <v>23</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2092,7 @@
         <v>4</v>
       </c>
       <c r="AH9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI9" t="n">
         <v>1</v>
@@ -2043,7 +2110,7 @@
         <v>19</v>
       </c>
       <c r="AN9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO9" t="n">
         <v>6</v>
@@ -2079,7 +2146,7 @@
         <v>28</v>
       </c>
       <c r="AZ9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA9" t="n">
         <v>3</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-5.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="n">
         <v>26</v>
@@ -2207,7 +2274,7 @@
         <v>26</v>
       </c>
       <c r="AH10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
         <v>24</v>
@@ -2222,10 +2289,10 @@
         <v>23</v>
       </c>
       <c r="AM10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO10" t="n">
         <v>23</v>
@@ -2261,7 +2328,7 @@
         <v>20</v>
       </c>
       <c r="AZ10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA10" t="n">
         <v>16</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -2299,37 +2366,37 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E11" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F11" t="n">
         <v>32</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="J11" t="n">
         <v>83.09999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L11" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M11" t="n">
         <v>19.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4</v>
+        <v>0.399</v>
       </c>
       <c r="O11" t="n">
         <v>17</v>
@@ -2338,19 +2405,19 @@
         <v>21.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.792</v>
+        <v>0.791</v>
       </c>
       <c r="R11" t="n">
         <v>10.8</v>
       </c>
       <c r="S11" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="T11" t="n">
-        <v>44.9</v>
+        <v>44.8</v>
       </c>
       <c r="U11" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="V11" t="n">
         <v>15.2</v>
@@ -2371,25 +2438,25 @@
         <v>19.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>100.9</v>
+        <v>100.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG11" t="n">
         <v>10</v>
       </c>
       <c r="AH11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI11" t="n">
         <v>9</v>
@@ -2410,10 +2477,10 @@
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ11" t="n">
         <v>4</v>
@@ -2437,22 +2504,22 @@
         <v>27</v>
       </c>
       <c r="AX11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ11" t="n">
         <v>28</v>
       </c>
       <c r="BA11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -2481,34 +2548,34 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F12" t="n">
         <v>33</v>
       </c>
       <c r="G12" t="n">
-        <v>0.548</v>
+        <v>0.542</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
       </c>
       <c r="I12" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="J12" t="n">
         <v>82.5</v>
       </c>
       <c r="K12" t="n">
-        <v>0.461</v>
+        <v>0.462</v>
       </c>
       <c r="L12" t="n">
         <v>10.6</v>
       </c>
       <c r="M12" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="N12" t="n">
         <v>0.369</v>
@@ -2526,16 +2593,16 @@
         <v>11</v>
       </c>
       <c r="S12" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="T12" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="U12" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="V12" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="W12" t="n">
         <v>8.5</v>
@@ -2550,16 +2617,16 @@
         <v>20.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>105.9</v>
+        <v>106</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE12" t="n">
         <v>12</v>
@@ -2610,7 +2677,7 @@
         <v>9</v>
       </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV12" t="n">
         <v>30</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E13" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F13" t="n">
         <v>27</v>
       </c>
       <c r="G13" t="n">
-        <v>0.635</v>
+        <v>0.63</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
@@ -2687,34 +2754,34 @@
         <v>0.435</v>
       </c>
       <c r="L13" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M13" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="O13" t="n">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="P13" t="n">
-        <v>23.3</v>
+        <v>23</v>
       </c>
       <c r="Q13" t="n">
         <v>0.75</v>
       </c>
       <c r="R13" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="S13" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="T13" t="n">
         <v>46.4</v>
       </c>
       <c r="U13" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V13" t="n">
         <v>15.1</v>
@@ -2732,16 +2799,16 @@
         <v>20.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>94.90000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="AC13" t="n">
         <v>5.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2750,7 +2817,7 @@
         <v>8</v>
       </c>
       <c r="AG13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH13" t="n">
         <v>12</v>
@@ -2771,13 +2838,13 @@
         <v>15</v>
       </c>
       <c r="AN13" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AO13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AP13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ13" t="n">
         <v>18</v>
@@ -2795,10 +2862,10 @@
         <v>27</v>
       </c>
       <c r="AV13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX13" t="n">
         <v>3</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -2845,49 +2912,49 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E14" t="n">
         <v>49</v>
       </c>
       <c r="F14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G14" t="n">
-        <v>0.662</v>
+        <v>0.671</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="J14" t="n">
         <v>80.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.476</v>
+        <v>0.477</v>
       </c>
       <c r="L14" t="n">
         <v>7.6</v>
       </c>
       <c r="M14" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="N14" t="n">
         <v>0.356</v>
       </c>
       <c r="O14" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="P14" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.708</v>
+        <v>0.707</v>
       </c>
       <c r="R14" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S14" t="n">
         <v>30</v>
@@ -2896,7 +2963,7 @@
         <v>41.4</v>
       </c>
       <c r="U14" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="V14" t="n">
         <v>14.8</v>
@@ -2911,28 +2978,28 @@
         <v>4.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>100.6</v>
+        <v>100.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
       </c>
       <c r="AF14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AG14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH14" t="n">
         <v>28</v>
@@ -2956,7 +3023,7 @@
         <v>19</v>
       </c>
       <c r="AO14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP14" t="n">
         <v>9</v>
@@ -2968,7 +3035,7 @@
         <v>15</v>
       </c>
       <c r="AS14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT14" t="n">
         <v>19</v>
@@ -2977,7 +3044,7 @@
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -2989,13 +3056,13 @@
         <v>5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA14" t="n">
         <v>8</v>
       </c>
       <c r="BB14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC14" t="n">
         <v>4</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -3027,22 +3094,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F15" t="n">
         <v>36</v>
       </c>
       <c r="G15" t="n">
-        <v>0.514</v>
+        <v>0.507</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J15" t="n">
         <v>81.3</v>
@@ -3054,61 +3121,61 @@
         <v>8.800000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="N15" t="n">
         <v>0.358</v>
       </c>
       <c r="O15" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="P15" t="n">
         <v>27.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="R15" t="n">
         <v>11.5</v>
       </c>
       <c r="S15" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="T15" t="n">
         <v>44.7</v>
       </c>
       <c r="U15" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="V15" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W15" t="n">
         <v>7.1</v>
       </c>
       <c r="X15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z15" t="n">
         <v>18.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.4</v>
+        <v>102.3</v>
       </c>
       <c r="AC15" t="n">
         <v>0.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF15" t="n">
         <v>15</v>
@@ -3123,7 +3190,7 @@
         <v>14</v>
       </c>
       <c r="AJ15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK15" t="n">
         <v>10</v>
@@ -3150,13 +3217,13 @@
         <v>13</v>
       </c>
       <c r="AS15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT15" t="n">
         <v>3</v>
       </c>
       <c r="AU15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV15" t="n">
         <v>24</v>
@@ -3171,7 +3238,7 @@
         <v>16</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BA15" t="n">
         <v>1</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F16" t="n">
         <v>24</v>
       </c>
       <c r="G16" t="n">
-        <v>0.671</v>
+        <v>0.667</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
@@ -3227,7 +3294,7 @@
         <v>36.3</v>
       </c>
       <c r="J16" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="K16" t="n">
         <v>0.444</v>
@@ -3239,31 +3306,31 @@
         <v>13.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0.348</v>
+        <v>0.346</v>
       </c>
       <c r="O16" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="P16" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
       <c r="R16" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="S16" t="n">
         <v>29.4</v>
       </c>
       <c r="T16" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="U16" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V16" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W16" t="n">
         <v>8.5</v>
@@ -3272,31 +3339,31 @@
         <v>5.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA16" t="n">
         <v>19.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.8</v>
+        <v>93.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF16" t="n">
         <v>4</v>
       </c>
       <c r="AG16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH16" t="n">
         <v>17</v>
@@ -3305,10 +3372,10 @@
         <v>21</v>
       </c>
       <c r="AJ16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3320,10 +3387,10 @@
         <v>23</v>
       </c>
       <c r="AO16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ16" t="n">
         <v>7</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>8</v>
       </c>
       <c r="AD17" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3505,7 +3572,7 @@
         <v>8</v>
       </c>
       <c r="AP17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ17" t="n">
         <v>15</v>
@@ -3514,7 +3581,7 @@
         <v>28</v>
       </c>
       <c r="AS17" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -3573,52 +3640,52 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E18" t="n">
         <v>35</v>
       </c>
       <c r="F18" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G18" t="n">
-        <v>0.486</v>
+        <v>0.493</v>
       </c>
       <c r="H18" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I18" t="n">
         <v>38.2</v>
       </c>
       <c r="J18" t="n">
-        <v>87.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="K18" t="n">
         <v>0.436</v>
       </c>
       <c r="L18" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M18" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0.356</v>
+        <v>0.355</v>
       </c>
       <c r="O18" t="n">
         <v>15.6</v>
       </c>
       <c r="P18" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.74</v>
+        <v>0.739</v>
       </c>
       <c r="R18" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="S18" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T18" t="n">
         <v>43.9</v>
@@ -3627,16 +3694,16 @@
         <v>22.8</v>
       </c>
       <c r="V18" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W18" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="X18" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z18" t="n">
         <v>19.1</v>
@@ -3648,19 +3715,19 @@
         <v>98.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>-1.5</v>
+        <v>-1.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AE18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG18" t="n">
         <v>17</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>18</v>
       </c>
       <c r="AH18" t="n">
         <v>16</v>
@@ -3672,22 +3739,22 @@
         <v>1</v>
       </c>
       <c r="AK18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL18" t="n">
         <v>17</v>
       </c>
       <c r="AM18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AN18" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AO18" t="n">
         <v>24</v>
       </c>
       <c r="AP18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ18" t="n">
         <v>20</v>
@@ -3705,7 +3772,7 @@
         <v>12</v>
       </c>
       <c r="AV18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW18" t="n">
         <v>11</v>
@@ -3720,7 +3787,7 @@
         <v>9</v>
       </c>
       <c r="BA18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB18" t="n">
         <v>12</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E19" t="n">
         <v>26</v>
       </c>
       <c r="F19" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G19" t="n">
-        <v>0.361</v>
+        <v>0.366</v>
       </c>
       <c r="H19" t="n">
         <v>48.1</v>
@@ -3773,7 +3840,7 @@
         <v>35.8</v>
       </c>
       <c r="J19" t="n">
-        <v>81.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="K19" t="n">
         <v>0.438</v>
@@ -3788,13 +3855,13 @@
         <v>0.3</v>
       </c>
       <c r="O19" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="P19" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.732</v>
+        <v>0.733</v>
       </c>
       <c r="R19" t="n">
         <v>12.3</v>
@@ -3803,7 +3870,7 @@
         <v>30.3</v>
       </c>
       <c r="T19" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="U19" t="n">
         <v>22.1</v>
@@ -3812,10 +3879,10 @@
         <v>15</v>
       </c>
       <c r="W19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X19" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y19" t="n">
         <v>6</v>
@@ -3824,34 +3891,34 @@
         <v>18.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>95.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.6</v>
+        <v>-2.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AE19" t="n">
         <v>23</v>
       </c>
       <c r="AF19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG19" t="n">
         <v>23</v>
       </c>
       <c r="AH19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
@@ -3872,10 +3939,10 @@
         <v>6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AR19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS19" t="n">
         <v>17</v>
@@ -3884,10 +3951,10 @@
         <v>11</v>
       </c>
       <c r="AU19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV19" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AW19" t="n">
         <v>12</v>
@@ -3896,7 +3963,7 @@
         <v>18</v>
       </c>
       <c r="AY19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ19" t="n">
         <v>7</v>
@@ -3908,7 +3975,7 @@
         <v>20</v>
       </c>
       <c r="BC19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-3.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AE20" t="n">
         <v>25</v>
@@ -4054,7 +4121,7 @@
         <v>28</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR20" t="n">
         <v>12</v>
@@ -4063,7 +4130,7 @@
         <v>25</v>
       </c>
       <c r="AT20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU20" t="n">
         <v>22</v>
@@ -4078,7 +4145,7 @@
         <v>8</v>
       </c>
       <c r="AY20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ20" t="n">
         <v>19</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>3.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE21" t="n">
         <v>8</v>
@@ -4206,7 +4273,7 @@
         <v>7</v>
       </c>
       <c r="AG21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH21" t="n">
         <v>30</v>
@@ -4215,10 +4282,10 @@
         <v>23</v>
       </c>
       <c r="AJ21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4245,7 +4312,7 @@
         <v>24</v>
       </c>
       <c r="AT21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU21" t="n">
         <v>29</v>
@@ -4254,7 +4321,7 @@
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E22" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F22" t="n">
         <v>20</v>
       </c>
       <c r="G22" t="n">
-        <v>0.73</v>
+        <v>0.726</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4325,34 +4392,34 @@
         <v>0.481</v>
       </c>
       <c r="L22" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M22" t="n">
         <v>19.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0.376</v>
+        <v>0.378</v>
       </c>
       <c r="O22" t="n">
         <v>22.8</v>
       </c>
       <c r="P22" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.827</v>
+        <v>0.828</v>
       </c>
       <c r="R22" t="n">
         <v>10.3</v>
       </c>
       <c r="S22" t="n">
-        <v>33.2</v>
+        <v>33.1</v>
       </c>
       <c r="T22" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="U22" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="V22" t="n">
         <v>15.6</v>
@@ -4361,7 +4428,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="X22" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="Y22" t="n">
         <v>4</v>
@@ -4379,7 +4446,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -4406,7 +4473,7 @@
         <v>13</v>
       </c>
       <c r="AM22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN22" t="n">
         <v>5</v>
@@ -4424,10 +4491,10 @@
         <v>25</v>
       </c>
       <c r="AS22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU22" t="n">
         <v>21</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E23" t="n">
         <v>19</v>
       </c>
       <c r="F23" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G23" t="n">
-        <v>0.257</v>
+        <v>0.26</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
@@ -4501,46 +4568,46 @@
         <v>37.8</v>
       </c>
       <c r="J23" t="n">
-        <v>83.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="K23" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L23" t="n">
         <v>6.4</v>
       </c>
       <c r="M23" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0.33</v>
+        <v>0.331</v>
       </c>
       <c r="O23" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="P23" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.763</v>
+        <v>0.766</v>
       </c>
       <c r="R23" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S23" t="n">
         <v>31.6</v>
       </c>
       <c r="T23" t="n">
-        <v>42.3</v>
+        <v>42.1</v>
       </c>
       <c r="U23" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="V23" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W23" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="X23" t="n">
         <v>4.2</v>
@@ -4549,10 +4616,10 @@
         <v>5.1</v>
       </c>
       <c r="Z23" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="AB23" t="n">
         <v>94.40000000000001</v>
@@ -4561,7 +4628,7 @@
         <v>-6.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4576,10 +4643,10 @@
         <v>25</v>
       </c>
       <c r="AI23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AK23" t="n">
         <v>14</v>
@@ -4588,7 +4655,7 @@
         <v>20</v>
       </c>
       <c r="AM23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN23" t="n">
         <v>28</v>
@@ -4600,7 +4667,7 @@
         <v>30</v>
       </c>
       <c r="AQ23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR23" t="n">
         <v>24</v>
@@ -4612,10 +4679,10 @@
         <v>15</v>
       </c>
       <c r="AU23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV23" t="n">
         <v>10</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>11</v>
       </c>
       <c r="AW23" t="n">
         <v>30</v>
@@ -4627,13 +4694,13 @@
         <v>18</v>
       </c>
       <c r="AZ23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC23" t="n">
         <v>29</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F24" t="n">
         <v>43</v>
       </c>
       <c r="G24" t="n">
-        <v>0.411</v>
+        <v>0.403</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
@@ -4683,37 +4750,37 @@
         <v>37.4</v>
       </c>
       <c r="J24" t="n">
-        <v>83.8</v>
+        <v>84</v>
       </c>
       <c r="K24" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L24" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M24" t="n">
         <v>17.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0.36</v>
+        <v>0.361</v>
       </c>
       <c r="O24" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="P24" t="n">
-        <v>16.7</v>
+        <v>16.5</v>
       </c>
       <c r="Q24" t="n">
         <v>0.72</v>
       </c>
       <c r="R24" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S24" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="T24" t="n">
-        <v>41.2</v>
+        <v>41.4</v>
       </c>
       <c r="U24" t="n">
         <v>23</v>
@@ -4725,25 +4792,25 @@
         <v>7.3</v>
       </c>
       <c r="X24" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y24" t="n">
         <v>4.9</v>
       </c>
       <c r="Z24" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>93</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AC24" t="n">
-        <v>-3.3</v>
+        <v>-3.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE24" t="n">
         <v>20</v>
@@ -4761,7 +4828,7 @@
         <v>13</v>
       </c>
       <c r="AJ24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK24" t="n">
         <v>18</v>
@@ -4791,10 +4858,10 @@
         <v>16</v>
       </c>
       <c r="AT24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AV24" t="n">
         <v>2</v>
@@ -4809,7 +4876,7 @@
         <v>13</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E25" t="n">
         <v>23</v>
       </c>
       <c r="F25" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G25" t="n">
-        <v>0.311</v>
+        <v>0.315</v>
       </c>
       <c r="H25" t="n">
         <v>48.3</v>
@@ -4865,7 +4932,7 @@
         <v>37.1</v>
       </c>
       <c r="J25" t="n">
-        <v>84.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K25" t="n">
         <v>0.44</v>
@@ -4874,19 +4941,19 @@
         <v>5.7</v>
       </c>
       <c r="M25" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0.323</v>
+        <v>0.322</v>
       </c>
       <c r="O25" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="P25" t="n">
         <v>19.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.735</v>
+        <v>0.732</v>
       </c>
       <c r="R25" t="n">
         <v>11.8</v>
@@ -4895,10 +4962,10 @@
         <v>29.9</v>
       </c>
       <c r="T25" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="U25" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="V25" t="n">
         <v>15.4</v>
@@ -4913,19 +4980,19 @@
         <v>5</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA25" t="n">
         <v>18.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>94.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC25" t="n">
         <v>-6.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
         <v>27</v>
@@ -4937,7 +5004,7 @@
         <v>27</v>
       </c>
       <c r="AH25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI25" t="n">
         <v>15</v>
@@ -4952,7 +5019,7 @@
         <v>27</v>
       </c>
       <c r="AM25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN25" t="n">
         <v>29</v>
@@ -4964,7 +5031,7 @@
         <v>26</v>
       </c>
       <c r="AQ25" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AR25" t="n">
         <v>11</v>
@@ -4991,13 +5058,13 @@
         <v>17</v>
       </c>
       <c r="AZ25" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA25" t="n">
         <v>27</v>
       </c>
       <c r="BB25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC25" t="n">
         <v>28</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E26" t="n">
         <v>33</v>
       </c>
       <c r="F26" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G26" t="n">
-        <v>0.452</v>
+        <v>0.458</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
@@ -5050,7 +5117,7 @@
         <v>82</v>
       </c>
       <c r="K26" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L26" t="n">
         <v>8.300000000000001</v>
@@ -5062,13 +5129,13 @@
         <v>0.357</v>
       </c>
       <c r="O26" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="P26" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.777</v>
+        <v>0.776</v>
       </c>
       <c r="R26" t="n">
         <v>11</v>
@@ -5083,7 +5150,7 @@
         <v>21.7</v>
       </c>
       <c r="V26" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W26" t="n">
         <v>6.7</v>
@@ -5098,16 +5165,16 @@
         <v>18.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AB26" t="n">
         <v>98.09999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.1</v>
+        <v>-1.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE26" t="n">
         <v>19</v>
@@ -5119,16 +5186,16 @@
         <v>19</v>
       </c>
       <c r="AH26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ26" t="n">
         <v>13</v>
       </c>
       <c r="AK26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL26" t="n">
         <v>6</v>
@@ -5146,7 +5213,7 @@
         <v>25</v>
       </c>
       <c r="AQ26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR26" t="n">
         <v>19</v>
@@ -5161,13 +5228,13 @@
         <v>19</v>
       </c>
       <c r="AV26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW26" t="n">
         <v>28</v>
       </c>
       <c r="AX26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY26" t="n">
         <v>6</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E27" t="n">
         <v>27</v>
       </c>
       <c r="F27" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G27" t="n">
-        <v>0.365</v>
+        <v>0.37</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
@@ -5229,7 +5296,7 @@
         <v>37.6</v>
       </c>
       <c r="J27" t="n">
-        <v>83.8</v>
+        <v>83.7</v>
       </c>
       <c r="K27" t="n">
         <v>0.449</v>
@@ -5241,19 +5308,19 @@
         <v>20.1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.366</v>
+        <v>0.367</v>
       </c>
       <c r="O27" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="P27" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="R27" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="S27" t="n">
         <v>29</v>
@@ -5268,7 +5335,7 @@
         <v>14.8</v>
       </c>
       <c r="W27" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X27" t="n">
         <v>4.2</v>
@@ -5277,10 +5344,10 @@
         <v>6.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB27" t="n">
         <v>100</v>
@@ -5289,13 +5356,13 @@
         <v>-4.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="n">
         <v>21</v>
       </c>
       <c r="AF27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG27" t="n">
         <v>22</v>
@@ -5310,7 +5377,7 @@
         <v>8</v>
       </c>
       <c r="AK27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL27" t="n">
         <v>12</v>
@@ -5322,7 +5389,7 @@
         <v>9</v>
       </c>
       <c r="AO27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP27" t="n">
         <v>12</v>
@@ -5343,13 +5410,13 @@
         <v>25</v>
       </c>
       <c r="AV27" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AW27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY27" t="n">
         <v>27</v>
@@ -5358,7 +5425,7 @@
         <v>25</v>
       </c>
       <c r="BA27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>7.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -5504,10 +5571,10 @@
         <v>3</v>
       </c>
       <c r="AO28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ28" t="n">
         <v>3</v>
@@ -5525,10 +5592,10 @@
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AE29" t="n">
         <v>21</v>
@@ -5686,7 +5753,7 @@
         <v>26</v>
       </c>
       <c r="AO29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP29" t="n">
         <v>15</v>
@@ -5701,7 +5768,7 @@
         <v>27</v>
       </c>
       <c r="AT29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU29" t="n">
         <v>20</v>
@@ -5716,7 +5783,7 @@
         <v>21</v>
       </c>
       <c r="AY29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -5757,37 +5824,37 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E30" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F30" t="n">
         <v>36</v>
       </c>
       <c r="G30" t="n">
-        <v>0.514</v>
+        <v>0.507</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
       </c>
       <c r="I30" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J30" t="n">
         <v>82.09999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.453</v>
+        <v>0.451</v>
       </c>
       <c r="L30" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M30" t="n">
         <v>16.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0.364</v>
+        <v>0.361</v>
       </c>
       <c r="O30" t="n">
         <v>18.1</v>
@@ -5796,22 +5863,22 @@
         <v>23.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.765</v>
+        <v>0.766</v>
       </c>
       <c r="R30" t="n">
         <v>12.4</v>
       </c>
       <c r="S30" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T30" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="U30" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="V30" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W30" t="n">
         <v>8.4</v>
@@ -5820,25 +5887,25 @@
         <v>6.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>98.40000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF30" t="n">
         <v>15</v>
@@ -5850,7 +5917,7 @@
         <v>6</v>
       </c>
       <c r="AI30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ30" t="n">
         <v>11</v>
@@ -5865,7 +5932,7 @@
         <v>28</v>
       </c>
       <c r="AN30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO30" t="n">
         <v>7</v>
@@ -5874,13 +5941,13 @@
         <v>8</v>
       </c>
       <c r="AQ30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
         <v>7</v>
       </c>
       <c r="AS30" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AT30" t="n">
         <v>13</v>
@@ -5889,16 +5956,16 @@
         <v>13</v>
       </c>
       <c r="AV30" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX30" t="n">
         <v>5</v>
       </c>
       <c r="AY30" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AZ30" t="n">
         <v>29</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
@@ -6017,16 +6084,16 @@
         <v>-2.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AE31" t="n">
         <v>23</v>
       </c>
       <c r="AF31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH31" t="n">
         <v>8</v>
@@ -6047,13 +6114,13 @@
         <v>20</v>
       </c>
       <c r="AN31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO31" t="n">
         <v>25</v>
       </c>
       <c r="AP31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ31" t="n">
         <v>21</v>
@@ -6080,19 +6147,19 @@
         <v>24</v>
       </c>
       <c r="AY31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB31" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BC31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-30-2012-13</t>
+          <t>2013-03-30</t>
         </is>
       </c>
     </row>
